--- a/src/attributions/attributions_ig_traj_47.xlsx
+++ b/src/attributions/attributions_ig_traj_47.xlsx
@@ -999,10 +999,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.7009479577909679</v>
+        <v>-0.3055639048466909</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
@@ -1011,13 +1011,13 @@
         <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07286192408997956</v>
+        <v>-0.05382789704065479</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7009815577052405</v>
+        <v>0.2303271448660869</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1029,7 +1029,7 @@
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9077202536082086</v>
+        <v>-0.577163674498926</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -1038,52 +1038,52 @@
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.04429051729544002</v>
+        <v>0.02855940864575634</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9309492570381545</v>
+        <v>0.4472599598166206</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1702158981345139</v>
+        <v>-0.1376283497557311</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
         <v>-0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1096352672266177</v>
+        <v>0.09484910038654011</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2887164977770482</v>
+        <v>0.177180100599164</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.29333156618045</v>
+        <v>-0.0514033447041893</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
@@ -1092,16 +1092,16 @@
         <v>-0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.04481188811869768</v>
+        <v>0.1151112382163902</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.06710870051309435</v>
+        <v>0.03494060731592193</v>
       </c>
       <c r="AH2" t="n">
         <v>-0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -1110,22 +1110,22 @@
         <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.1150549509997126</v>
+        <v>-0.1130109130481625</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
         <v>-0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.1552424727134165</v>
+        <v>-0.1182425504772971</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3564830110711135</v>
+        <v>0.1917314244726414</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1134,22 +1134,22 @@
         <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-1.199133872248715</v>
+        <v>-1.153629780897003</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
         <v>-0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.3340709118861154</v>
+        <v>-0.1354055363283191</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.475921281603873</v>
+        <v>0.7006100699453428</v>
       </c>
       <c r="AZ2" t="n">
         <v>-0</v>
@@ -1158,13 +1158,13 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.3085614251188836</v>
+        <v>0.23108889673571</v>
       </c>
       <c r="BE2" t="n">
         <v>-0</v>
@@ -1173,43 +1173,43 @@
         <v>-0</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.0309154559387817</v>
+        <v>0.09609567174239991</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.1811670808097239</v>
+        <v>0.007865923692853501</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.3104823829655481</v>
+        <v>-0.09496512377052554</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.1419410578183443</v>
+        <v>-0.2293233279154834</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.1475867219361249</v>
+        <v>0.04522313216788981</v>
       </c>
       <c r="BR2" t="n">
         <v>-0</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
         <v>-0</v>
@@ -1218,7 +1218,7 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.5997356246551363</v>
+        <v>-0.6489479555940478</v>
       </c>
       <c r="BW2" t="n">
         <v>-0</v>
@@ -1227,10 +1227,10 @@
         <v>-0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.26966403755526</v>
+        <v>0.01654508188248413</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.6169575812047832</v>
+        <v>0.4689174225432911</v>
       </c>
       <c r="CA2" t="n">
         <v>0</v>
@@ -1245,22 +1245,22 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.3355245271742304</v>
+        <v>0.2701225429368335</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.0154632059114157</v>
+        <v>0.0235022064451178</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0.2798855044023071</v>
+        <v>-0.1739899857733802</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK2" t="n">
         <v>-0</v>
@@ -1272,25 +1272,25 @@
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.1203703165724157</v>
+        <v>0.1812384694691668</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP2" t="n">
         <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.03761716596554194</v>
+        <v>-0.03626143782737078</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.006078565510440525</v>
+        <v>-0.1363694174110532</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>0</v>
@@ -1299,22 +1299,22 @@
         <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.2844447250488075</v>
+        <v>0.2651637269186768</v>
       </c>
       <c r="CX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY2" t="n">
         <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.02415534684394079</v>
+        <v>0.01129853010284225</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0.2972551038080262</v>
+        <v>-0.157185562546493</v>
       </c>
       <c r="DB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="n">
         <v>0</v>
@@ -1326,19 +1326,19 @@
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1445440870749505</v>
+        <v>-0.0073082110920264</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
         <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.07525888616141146</v>
+        <v>0.06258990076079307</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-0.2979587990430289</v>
+        <v>-0.0516774954450516</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
@@ -1347,25 +1347,25 @@
         <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.1257374473656155</v>
+        <v>-0.02248381991012195</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
         <v>-0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.106161786824168</v>
+        <v>-0.03056591009955858</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.1866679693759105</v>
+        <v>-0.1079081887816241</v>
       </c>
       <c r="DT2" t="n">
         <v>-0</v>
@@ -1374,58 +1374,58 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.2922337110552514</v>
+        <v>0.1298882678747104</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.1877145327932532</v>
+        <v>-0.01348138004638308</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.04157661729515442</v>
+        <v>0.05021327572330942</v>
       </c>
       <c r="EC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED2" t="n">
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.2237032863053404</v>
+        <v>0.09475142228515965</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.1862306046191418</v>
+        <v>-0.01556549890339774</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0.08463976800328549</v>
+        <v>0.01795387125396091</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
         <v>0</v>
@@ -1434,25 +1434,25 @@
         <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.1261228725970559</v>
+        <v>0.1572805149894583</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
         <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.1033129371594117</v>
+        <v>0.1596251692055848</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.06376324824775988</v>
+        <v>-0.00858341330460833</v>
       </c>
       <c r="EU2" t="n">
         <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
@@ -1461,61 +1461,61 @@
         <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.2974153419880705</v>
+        <v>0.3007919939541015</v>
       </c>
       <c r="EZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="n">
         <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.03028879069041322</v>
+        <v>0.06095059310311315</v>
       </c>
       <c r="FC2" t="n">
-        <v>-0.27439266167432</v>
+        <v>-0.1843308103785647</v>
       </c>
       <c r="FD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE2" t="n">
         <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.04153454754211395</v>
+        <v>0.2481304940681981</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
         <v>0</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.1413352550777106</v>
+        <v>-0.02621077702062739</v>
       </c>
       <c r="FL2" t="n">
-        <v>-0.4094650538169874</v>
+        <v>-0.2434029335866257</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.1547649196577439</v>
+        <v>0.374905069648266</v>
       </c>
       <c r="FR2" t="n">
         <v>0</v>
@@ -1524,66 +1524,66 @@
         <v>0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.1355027145961601</v>
+        <v>-0.08478658348033627</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.002897655044798855</v>
+        <v>0.002542278090151096</v>
       </c>
       <c r="FV2" t="n">
         <v>0</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
         <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.07720050399758996</v>
+        <v>0.1350965079280403</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
         <v>0</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.1463952272684299</v>
+        <v>0.02302243204674632</v>
       </c>
       <c r="GE2" t="n">
         <v>0</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.391955545684283</v>
+        <v>-0.1699917291460208</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1273708655117334</v>
+        <v>0.03335002511072459</v>
       </c>
       <c r="F3" t="n">
-        <v>0.620471528060512</v>
+        <v>0.1957139542607474</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1598,19 +1598,19 @@
         <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5156046586982046</v>
+        <v>-0.351904571504832</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04437713561736732</v>
+        <v>0.1803322319151887</v>
       </c>
       <c r="O3" t="n">
-        <v>1.010717757176399</v>
+        <v>0.3221652699923002</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
@@ -1622,10 +1622,10 @@
         <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1161989564919185</v>
+        <v>-0.1109636527664556</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
@@ -1634,10 +1634,10 @@
         <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1560184537589657</v>
+        <v>0.1386763974956005</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03059145362643238</v>
+        <v>0.05730784580425741</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1652,25 +1652,25 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.1306974235603985</v>
+        <v>-0.02296479317437627</v>
       </c>
       <c r="AD3" t="n">
         <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.1242654272165531</v>
+        <v>0.246353527235508</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.02744629830122277</v>
+        <v>0.1830115621364951</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1679,22 +1679,22 @@
         <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.11025164220043</v>
+        <v>-0.178058296681319</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN3" t="n">
         <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.07250151370140137</v>
+        <v>-0.06916979184982873</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1751299699702346</v>
+        <v>0.1399370803222277</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1703,10 +1703,10 @@
         <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.760498100017964</v>
+        <v>-0.7070949415054113</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1715,10 +1715,10 @@
         <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.3726415525744893</v>
+        <v>0.114165058290429</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.9185401104281107</v>
+        <v>0.1904082346786442</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
@@ -1727,13 +1727,13 @@
         <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.2285284480392822</v>
+        <v>0.0993188758455856</v>
       </c>
       <c r="BE3" t="n">
         <v>-0</v>
@@ -1742,13 +1742,13 @@
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.07248532200953103</v>
+        <v>0.1589132837382365</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1658584737898537</v>
+        <v>0.138227808947156</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
@@ -1757,25 +1757,25 @@
         <v>-0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.208883634768884</v>
+        <v>-0.01887479349014282</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.005983730022120745</v>
+        <v>-0.1265190505929345</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.08968792377137975</v>
+        <v>-0.001318809891525488</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1787,22 +1787,22 @@
         <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.2324093972932063</v>
+        <v>-0.247886009683203</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
         <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2094173878945159</v>
+        <v>0.108514108704237</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.5708157087507504</v>
+        <v>0.2317602195282512</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
         <v>0</v>
@@ -1811,25 +1811,25 @@
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1719895128468164</v>
+        <v>0.1716170694672189</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01642269878518387</v>
+        <v>-0.05347753706188101</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.2354786977520215</v>
+        <v>-0.1341784868648905</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
@@ -1841,22 +1841,22 @@
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.00759687251095081</v>
+        <v>0.132874572533965</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.04376725573125746</v>
+        <v>-0.1012995535258569</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.02250319074659455</v>
+        <v>-0.09500743204307503</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
         <v>0</v>
@@ -1868,22 +1868,22 @@
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1374292421813904</v>
+        <v>0.1563399905626105</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.02601326990503279</v>
+        <v>-0.03285780539798691</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.2402767760731845</v>
+        <v>-0.1330444035217032</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1895,46 +1895,46 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.04473801790787544</v>
+        <v>0.02949028181859265</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.1838734915364397</v>
+        <v>0.1153126181231908</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.09569631166463141</v>
+        <v>-0.004710614684291373</v>
       </c>
       <c r="DK3" t="n">
         <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.02745938946589471</v>
+        <v>0.08545174493859332</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.07168336916711926</v>
+        <v>-0.0158925261381153</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.01842480996465788</v>
+        <v>-0.03658419614688541</v>
       </c>
       <c r="DT3" t="n">
         <v>0</v>
@@ -1943,28 +1943,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.1240614944718884</v>
+        <v>-0.06344592414986801</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.01269286712995079</v>
+        <v>0.01357637699842149</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.1149820792931666</v>
+        <v>-0.096473839835529</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
         <v>-0</v>
@@ -1973,37 +1973,37 @@
         <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.1415211924889588</v>
+        <v>0.05018095530027669</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.1029769497679561</v>
+        <v>0.01791411769809705</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.2779220852636857</v>
+        <v>-0.04667021084485905</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.02727831570230112</v>
+        <v>0.05586399699894303</v>
       </c>
       <c r="EQ3" t="n">
         <v>-0</v>
@@ -2012,40 +2012,40 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.09850235095273356</v>
+        <v>0.06132168600766287</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.08322588838038104</v>
+        <v>-0.09387290112214312</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.1254682096992089</v>
+        <v>0.1814515916314953</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.03066139736234122</v>
+        <v>-0.02485210894097335</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0.2176999179367737</v>
+        <v>-0.1283047088178366</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2057,34 +2057,34 @@
         <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.1050148429918384</v>
+        <v>0.1929768193198946</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.0298519467090482</v>
+        <v>-0.09103030497231074</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.1100777220773365</v>
+        <v>0.1171859798504566</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.03658252029631837</v>
+        <v>0.04756452105308713</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,43 +2093,43 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.00115185117178783</v>
+        <v>0.0004409782433798839</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0.2402298624994415</v>
+        <v>-0.1404030487870274</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.01618208868470729</v>
+        <v>0.0440189090036141</v>
       </c>
       <c r="GA3" t="n">
         <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.06409192113912371</v>
+        <v>0.006615589235019101</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>-0</v>
@@ -2140,46 +2140,46 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2215294457763141</v>
+        <v>0.3766777487575211</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.07292556100962073</v>
+        <v>-0.1455406475900808</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03840936272460374</v>
+        <v>-0.07082135499817933</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2952741051727642</v>
+        <v>0.7220460762943672</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1389886555808135</v>
+        <v>-0.4694342106440199</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.07205261285037887</v>
+        <v>-0.2676418655702703</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -2188,22 +2188,22 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08319515716234173</v>
+        <v>0.1731822240260165</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.008112782759009875</v>
+        <v>-0.04486484917839326</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0862299729241931</v>
+        <v>-0.1915363423060021</v>
       </c>
       <c r="X4" t="n">
         <v>-0</v>
@@ -2212,82 +2212,82 @@
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.06290612005099692</v>
+        <v>0.1251445845521161</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.009947045032244318</v>
+        <v>-0.2581275197755136</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003756650413871604</v>
+        <v>-0.09432652171914087</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.008022506820783861</v>
+        <v>0.1991798306593575</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.07318639225217895</v>
+        <v>-0.05421424545163814</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.07819729714921661</v>
+        <v>-0.02126086039655552</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3435160781296537</v>
+        <v>0.8208803136650785</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.05254825076382121</v>
+        <v>-0.2445320607192726</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1244655343451792</v>
+        <v>-0.4727190951129448</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02887613403341349</v>
+        <v>-0.04975413887107406</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.04713903690923502</v>
+        <v>-0.09025744099818818</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.08400952520939282</v>
+        <v>0.05276701002644443</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,28 +2320,28 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.05747481498009885</v>
+        <v>0.1716161453810191</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0607326632919934</v>
+        <v>0.03036252176287664</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1944068900113273</v>
+        <v>0.1861326264491051</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
         <v>0</v>
@@ -2356,25 +2356,25 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1460796926760632</v>
+        <v>0.526898415022462</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01094654792689349</v>
+        <v>-0.1351949816338177</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.07893386959125862</v>
+        <v>-0.1715909749825325</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>-0</v>
@@ -2383,46 +2383,46 @@
         <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.09029763527997021</v>
+        <v>-0.1929731790934917</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.02530133048427583</v>
+        <v>0.1696576509781248</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.009589838271585214</v>
+        <v>0.03244778264996265</v>
       </c>
       <c r="CI4" t="n">
         <v>0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.009219293617409521</v>
+        <v>-0.1650260538247008</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.0448591618832721</v>
+        <v>0.1601465179245863</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.06084485668067902</v>
+        <v>0.01006617739189463</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2431,55 +2431,55 @@
         <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.07883664192597548</v>
+        <v>-0.1777043156419784</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.04801208190669863</v>
+        <v>0.1942199653261692</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.003055512558646003</v>
+        <v>0.01654336513280834</v>
       </c>
       <c r="DA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.03699421234084545</v>
+        <v>-0.06798548028793881</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.05527818634769013</v>
+        <v>0.1620820807924335</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.01630313676651526</v>
+        <v>-0.1728922514538394</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2488,28 +2488,28 @@
         <v>0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.004522031628229339</v>
+        <v>-0.1608505912419033</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.1391684627739203</v>
+        <v>-0.0588792093892614</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.03687881830634822</v>
+        <v>-0.0669544817659599</v>
       </c>
       <c r="DS4" t="n">
         <v>-0</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,16 +2518,16 @@
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.07134862358237747</v>
+        <v>-0.02857810083991762</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.002491310134305195</v>
+        <v>0.1331727871704446</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.02851595287307115</v>
+        <v>0.003241809707282485</v>
       </c>
       <c r="EB4" t="n">
         <v>0</v>
@@ -2536,25 +2536,25 @@
         <v>0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.1375760180555673</v>
+        <v>-0.08510729414874832</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>-0.1025672845417293</v>
+        <v>-0.3219736723658741</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.08960254769907625</v>
+        <v>-0.04538584201998093</v>
       </c>
       <c r="EK4" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,22 +2572,22 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.07518107642366693</v>
+        <v>-0.08273557411045065</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.06084202097550825</v>
+        <v>0.0319818980141027</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.01767931064032646</v>
+        <v>0.01528195756393183</v>
       </c>
       <c r="ET4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2599,49 +2599,49 @@
         <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.08188566440611109</v>
+        <v>-0.2333989360125249</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.02785583549192699</v>
+        <v>0.2039929521613185</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.008629177015525475</v>
+        <v>0.01595097315215781</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.04076639146552232</v>
+        <v>0.1225156999352775</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.06015192160813492</v>
+        <v>0.09642333752413491</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.04747773589569526</v>
+        <v>-0.06495994686431629</v>
       </c>
       <c r="FL4" t="n">
         <v>-0</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
         <v>0</v>
@@ -2650,25 +2650,25 @@
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.01082684880118945</v>
+        <v>-0.23187333705508</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.07927208760040438</v>
+        <v>0.2458682708214253</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.02400735243379538</v>
+        <v>0.2591523194917482</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
         <v>0</v>
@@ -2677,57 +2677,57 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.03534584341666373</v>
+        <v>-0.1014279229750036</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.06942736944916554</v>
+        <v>0.05336706075922738</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.4128976292903803</v>
+        <v>-0.3552542819432422</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2347462186786795</v>
+        <v>0.2518679340999524</v>
       </c>
       <c r="D5" t="n">
         <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1574777357017313</v>
+        <v>-0.0612597151322599</v>
       </c>
       <c r="F5" t="n">
         <v>-0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1447695482584417</v>
+        <v>-0.03778610632222709</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>-0</v>
@@ -2736,22 +2736,22 @@
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5461972268402872</v>
+        <v>-0.685975730240566</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3181004715462106</v>
+        <v>0.4533610690738045</v>
       </c>
       <c r="M5" t="n">
         <v>-0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2108840167708454</v>
+        <v>-0.06377311412130834</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2296174628121881</v>
+        <v>-0.02095293446386069</v>
       </c>
       <c r="Q5" t="n">
         <v>-0</v>
@@ -2763,184 +2763,184 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.07089822675712093</v>
+        <v>-0.08579888135242947</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04117169141305991</v>
+        <v>-0.1129412779471361</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1296556931569572</v>
+        <v>-0.1435276411452542</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04470744071871621</v>
+        <v>-0.02025612363317535</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.2423846936589006</v>
+        <v>-0.09219158566817348</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.001340973073021812</v>
+        <v>0.1587084411274342</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.04168582488341619</v>
+        <v>0.2260454701336529</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.1147558373131411</v>
+        <v>0.1640260224066217</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.08380803552539445</v>
+        <v>-0.2397794805515459</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.1010104112569713</v>
+        <v>0.03668504323985311</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.1533017790398531</v>
+        <v>-0.2070274146265812</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.04275335659903277</v>
+        <v>0.04018280991403465</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.5266751986778992</v>
+        <v>-0.6726238385340226</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.2496263866185371</v>
+        <v>0.02160567166408806</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.1263489086288088</v>
+        <v>-0.1935033036262581</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.3984603892701017</v>
+        <v>-0.05802298881922822</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.2106867836117908</v>
+        <v>0.1721720657448023</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.1275526465709202</v>
+        <v>0.2576155548094021</v>
       </c>
       <c r="BF5" t="n">
         <v>-0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.00753380437122339</v>
+        <v>0.1175969580879691</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.04560015982197758</v>
+        <v>0.02873719533754339</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL5" t="n">
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.1429732460735647</v>
+        <v>0.09379389549129551</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.08742186173179757</v>
+        <v>-0.02020999880922615</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.06514196589273696</v>
+        <v>-0.02218078975719746</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.01405421531790777</v>
+        <v>0.1378015062068807</v>
       </c>
       <c r="BS5" t="n">
         <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.1972521110101124</v>
+        <v>-0.3317014568154839</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.2939959978966352</v>
+        <v>0.01488313100603849</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.01194427554679071</v>
+        <v>-0.1749733419110775</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.1025374228729074</v>
+        <v>-0.03566701064910531</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2949,28 +2949,28 @@
         <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1620807446932567</v>
+        <v>0.2610441130328737</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.003903749908593334</v>
+        <v>-0.118321797200875</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0468072489204082</v>
+        <v>0.02678645996246062</v>
       </c>
       <c r="CI5" t="n">
         <v>0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.1371438943520568</v>
+        <v>-0.03400479909149337</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>0</v>
@@ -2979,52 +2979,52 @@
         <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.02520968671292398</v>
+        <v>0.1297726904953916</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.04827007999930594</v>
+        <v>-0.05049342424144766</v>
       </c>
       <c r="CP5" t="n">
         <v>0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.05054601072442669</v>
+        <v>-0.05906524010881115</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.05232584504842004</v>
+        <v>-0.05275855856304928</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.1585718232992757</v>
+        <v>0.2675419676271525</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.02607409553105339</v>
+        <v>-0.1186373728135389</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.08977675322816855</v>
+        <v>0.03206658793429923</v>
       </c>
       <c r="DA5" t="n">
         <v>-0</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.1158215670261881</v>
+        <v>-0.02653887495859777</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>-0</v>
@@ -3033,49 +3033,49 @@
         <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1783960541369028</v>
+        <v>0.03918698483160317</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.02123166488886312</v>
+        <v>-0.1769800405299835</v>
       </c>
       <c r="DH5" t="n">
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.100577437078933</v>
+        <v>0.4500291292659264</v>
       </c>
       <c r="DJ5" t="n">
         <v>0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.008857406421803809</v>
+        <v>0.02682631426149712</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.02895891218597415</v>
+        <v>0.08884376001020869</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.09197842967953181</v>
+        <v>-0.03904156240851576</v>
       </c>
       <c r="DQ5" t="n">
         <v>-0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.03645843210126842</v>
+        <v>0.06139669542555819</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.03888697571651805</v>
+        <v>-0.1368188324755407</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
@@ -3087,79 +3087,79 @@
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.2641898210250115</v>
+        <v>0.1936335716700859</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.00988062661872606</v>
+        <v>0.03072447373798698</v>
       </c>
       <c r="DZ5" t="n">
         <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.06455277662303081</v>
+        <v>0.1183547124325032</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.08431627934500005</v>
+        <v>0.18797037408226</v>
       </c>
       <c r="ED5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE5" t="n">
         <v>0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.05324310162355382</v>
+        <v>0.1385309444223127</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.01783998674311225</v>
+        <v>0.02486803791030335</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.002375225129163624</v>
+        <v>-0.02606928082363725</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0.1408266832990171</v>
+        <v>0.02852138187511449</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.144843738040132</v>
+        <v>0.2051622960248339</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.07968517167084974</v>
+        <v>-0.05156743784638657</v>
       </c>
       <c r="ER5" t="n">
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.1563383894713316</v>
+        <v>-0.009873566284016064</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.07110866300616059</v>
+        <v>0.03651076446188037</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW5" t="n">
         <v>0</v>
@@ -3168,25 +3168,25 @@
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.1498409865816004</v>
+        <v>0.3163083328616528</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.004111229863635557</v>
+        <v>-0.1122703129256214</v>
       </c>
       <c r="FA5" t="n">
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.08339301578183805</v>
+        <v>0.01254420716583021</v>
       </c>
       <c r="FC5" t="n">
         <v>0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0.1319544819826578</v>
+        <v>-0.02964467154207953</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>0</v>
@@ -3195,99 +3195,99 @@
         <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.09451040359646638</v>
+        <v>-0.1168577639778944</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0.01600931792502877</v>
+        <v>-0.188645708058295</v>
       </c>
       <c r="FJ5" t="n">
         <v>0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.03748931125646107</v>
+        <v>-0.02982299591479754</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.01406186783559648</v>
+        <v>0.2169761236943102</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.04998799891797678</v>
+        <v>0.1795416839002778</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0.1246682376683335</v>
+        <v>0.09454290473828231</v>
       </c>
       <c r="FS5" t="n">
         <v>0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.06685152128631958</v>
+        <v>-0.06353847112317991</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0.0002631093321151662</v>
+        <v>-0.01169032490663913</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
         <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.09763400758782255</v>
+        <v>0.2674604355772903</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.08259453845194875</v>
+        <v>0.1230935807047338</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC5" t="n">
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.07882311542406545</v>
+        <v>0.1567294883518115</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2037616855707687</v>
+        <v>0.01938591712247523</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.02111202638079063</v>
+        <v>-0.005815952733530489</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.07453040915224582</v>
+        <v>-0.006321023499902444</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3302,22 +3302,22 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2124493438443137</v>
+        <v>0.02895757289845605</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.02298014275549642</v>
+        <v>-0.009516742471455491</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1358135947513372</v>
+        <v>-0.01177386171358227</v>
       </c>
       <c r="O6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
@@ -3332,25 +3332,25 @@
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06370394910258421</v>
+        <v>0.007408857552449104</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00715562447599368</v>
+        <v>0.0006443501512808594</v>
       </c>
       <c r="V6" t="n">
         <v>-0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01093982352473709</v>
+        <v>0.008324744455993696</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -3359,52 +3359,52 @@
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06960918865395682</v>
+        <v>-0.002783366359043007</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0004503920305753802</v>
+        <v>-0.009678727344399066</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02386663544880818</v>
+        <v>-0.0091160803877988</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.05400979619187804</v>
+        <v>0.01580983242141603</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.002885308591349655</v>
+        <v>-0.001696157839010942</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.001542373569656463</v>
+        <v>0.0149648727109168</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
@@ -3413,25 +3413,25 @@
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2057405601822158</v>
+        <v>0.03212636278772488</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001097531130955906</v>
+        <v>-0.002369608020230948</v>
       </c>
       <c r="AW6" t="n">
         <v>-0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001330109680954264</v>
+        <v>-0.00564118107528329</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
@@ -3440,19 +3440,19 @@
         <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.04405664842636203</v>
+        <v>-0.004300688302097478</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.02565169247062719</v>
+        <v>-0.004965681788897455</v>
       </c>
       <c r="BF6" t="n">
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1011448406340567</v>
+        <v>-0.01256387757756859</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
@@ -3467,22 +3467,22 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.01488319929714037</v>
+        <v>0.0004647685475766495</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.003885603211754469</v>
+        <v>-0.002856063230777838</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02681290436986385</v>
+        <v>0.007223664720878127</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3494,16 +3494,16 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1234095953553566</v>
+        <v>0.02711626252166407</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.05577912347590719</v>
+        <v>-0.003336243989503536</v>
       </c>
       <c r="BX6" t="n">
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.004856229366250841</v>
+        <v>0.008941348621753512</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -3518,19 +3518,19 @@
         <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.07122285520437725</v>
+        <v>-0.01047559447709829</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0008877039067062208</v>
+        <v>0.00471218698986608</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.01569000951385753</v>
+        <v>0.003734376489106014</v>
       </c>
       <c r="CI6" t="n">
         <v>0</v>
@@ -3548,19 +3548,19 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.005064381418907848</v>
+        <v>-0.008023024274391017</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.004465978826537417</v>
+        <v>0.003170446984756561</v>
       </c>
       <c r="CP6" t="n">
         <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.01578341147630363</v>
+        <v>0.00166315735079369</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
@@ -3572,19 +3572,19 @@
         <v>0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.06741073908357149</v>
+        <v>-0.008725587349965898</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.01024663298676329</v>
+        <v>0.004184423034412578</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0006915745007767116</v>
+        <v>0.00195799261363263</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
@@ -3602,16 +3602,16 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0946185707682474</v>
+        <v>-0.002474414104898611</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.003410635528069239</v>
+        <v>0.002634869489367975</v>
       </c>
       <c r="DH6" t="n">
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.02254218818363217</v>
+        <v>-0.0008767279636834656</v>
       </c>
       <c r="DJ6" t="n">
         <v>-0</v>
@@ -3626,22 +3626,22 @@
         <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.03691057466195077</v>
+        <v>-0.006107946822850827</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.01160526093311547</v>
+        <v>-0.002824287589067227</v>
       </c>
       <c r="DQ6" t="n">
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.02722752154917827</v>
+        <v>0.007151599610833796</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3650,25 +3650,25 @@
         <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.05427311811087433</v>
+        <v>0.008244284861400716</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.004578340224248666</v>
+        <v>0.004032484085526445</v>
       </c>
       <c r="DZ6" t="n">
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.02546200788514089</v>
+        <v>-0.0075465614325482</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
         <v>0</v>
@@ -3680,19 +3680,19 @@
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0386073250226083</v>
+        <v>-0.002453062793012623</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0.005391510005268511</v>
+        <v>-0.0002344342530739109</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.03249880296707638</v>
+        <v>0.0005250211621889365</v>
       </c>
       <c r="EK6" t="n">
         <v>0</v>
@@ -3704,28 +3704,28 @@
         <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.04355050220434932</v>
+        <v>-0.009656725128069043</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.02539467715313222</v>
+        <v>-0.002119707093852378</v>
       </c>
       <c r="ER6" t="n">
         <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.03438668183436552</v>
+        <v>-0.002096908900793363</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>-0</v>
@@ -3734,19 +3734,19 @@
         <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.07053976692866877</v>
+        <v>-0.01060308952195746</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.001652809153096199</v>
+        <v>0.004253046531855556</v>
       </c>
       <c r="FA6" t="n">
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.009248683371999614</v>
+        <v>0.0009868910431247992</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
@@ -3764,52 +3764,52 @@
         <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.02176838330341586</v>
+        <v>-0.0008003625051733404</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0.0001830194439178256</v>
+        <v>0.008822503809556737</v>
       </c>
       <c r="FJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.04577881333404821</v>
+        <v>-0.0084338401739212</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.02634833274302657</v>
+        <v>-0.01556038327128378</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0148731690951812</v>
+        <v>0.004669411841273141</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.04452370605113253</v>
+        <v>0.007744555751278089</v>
       </c>
       <c r="FU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX6" t="n">
         <v>0</v>
@@ -3818,10 +3818,10 @@
         <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.00657073855393182</v>
+        <v>-0.007728857027640932</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.01205343400981358</v>
+        <v>-0.00564021587999568</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
@@ -3830,16 +3830,16 @@
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,7 +3847,7 @@
         <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7316497964849361</v>
+        <v>0.09757761094983913</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,25 +3856,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1504203808717845</v>
+        <v>-0.009824665861901082</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2478125178456526</v>
+        <v>-0.01450368606525083</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8208933052107177</v>
+        <v>0.1656726148294078</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,25 +3883,25 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2311488351659118</v>
+        <v>-0.04054185586052782</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.3479260319567859</v>
+        <v>-0.006038928862851419</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2141729787127018</v>
+        <v>0.02345635505928542</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,88 +3910,88 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.07214389403961539</v>
+        <v>-0.01988576789059593</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.1167806264512214</v>
+        <v>0.001411900979224597</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2078110202534718</v>
+        <v>-0.03796573098387846</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.07359300640673076</v>
+        <v>-0.03244484805817233</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.0335587736411025</v>
+        <v>0.0201189227465572</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.150986600878547</v>
+        <v>0.03383491830679402</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.06514462883925401</v>
+        <v>0.01488923527609277</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.07262809757700661</v>
+        <v>-0.01511916011531341</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.7537182816382747</v>
+        <v>0.1663464421931702</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.105320110723552</v>
+        <v>-0.02681604223203846</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -4000,16 +4000,16 @@
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.1720635169744985</v>
+        <v>0.004751906177449138</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.188747437584719</v>
+        <v>-0.007198749914782061</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,79 +4018,79 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.3107332143131121</v>
+        <v>-0.02721994392205762</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.1549181673341322</v>
+        <v>-0.02098837875274131</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.01471019285214604</v>
+        <v>0.002636661309614037</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.2303369133668126</v>
+        <v>0.03933040195717115</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.06669957886274705</v>
+        <v>0.02620365175056464</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.4579459178585492</v>
+        <v>0.1101942131791429</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.09146754569169431</v>
+        <v>-0.01479872811889521</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.1145634698028519</v>
+        <v>-0.009961327371820832</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.2200620739475095</v>
+        <v>-0.04447183478732588</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,37 +4099,37 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-2.84623692878538e-05</v>
+        <v>0.01212113248288962</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.1198573095767745</v>
+        <v>0.009752809541005032</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.04019479521914748</v>
+        <v>-0.03633331107018484</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.09851059397922572</v>
+        <v>0.01631205761356714</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,22 +4138,22 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.004513521845497038</v>
+        <v>0.006560787932244765</v>
       </c>
       <c r="CV7" t="n">
         <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.2106254066567632</v>
+        <v>-0.04622986886535319</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01319814886706306</v>
+        <v>0.004523044830878994</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
@@ -4165,25 +4165,25 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.1084204634958661</v>
+        <v>0.01023894258392583</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.3860335444746215</v>
+        <v>-0.03204091402384493</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06215665004210663</v>
+        <v>-0.008533743261384931</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4192,40 +4192,40 @@
         <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.04632315912626006</v>
+        <v>-0.0003088875521364118</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.07817088537638797</v>
+        <v>-0.01944579776823729</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.02523504565473022</v>
+        <v>0.03309878732703857</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.007381071188496106</v>
+        <v>0.0176963690190048</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.1399852493032584</v>
+        <v>0.01368524716570474</v>
       </c>
       <c r="DY7" t="n">
         <v>-0</v>
@@ -4234,10 +4234,10 @@
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.05888798190790111</v>
+        <v>-0.001206912833149594</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4246,25 +4246,25 @@
         <v>-0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.04767795582855436</v>
+        <v>-0.01045384833754833</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1342468974963269</v>
+        <v>-0.02253563088881311</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03119636325961404</v>
+        <v>-0.01537328313917171</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
@@ -4273,40 +4273,40 @@
         <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.163991562593833</v>
+        <v>0.002847922990024203</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.144718052127662</v>
+        <v>-0.03016084617831736</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.03491837295012512</v>
+        <v>-0.00547044442179326</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>-0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.03666684645873523</v>
+        <v>0.01695121094726356</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.2320760197343417</v>
+        <v>-0.04761050431764294</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,52 +4315,52 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.02924192806036417</v>
+        <v>0.0003099238861585297</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.07630994049075909</v>
+        <v>0.008213863441663834</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.128414093765179</v>
+        <v>-0.03920370870441226</v>
       </c>
       <c r="FI7" t="n">
         <v>0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.1122339145420345</v>
+        <v>-0.0009522527515419129</v>
       </c>
       <c r="FL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN7" t="n">
         <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01936776781749308</v>
+        <v>0.03415061105190867</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.1393094105116507</v>
+        <v>-0.08769355274952161</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,7 +4369,7 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.07219713600154107</v>
+        <v>-0.01421421016979062</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
@@ -4381,13 +4381,13 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-0.02283278273335787</v>
+        <v>-0.005107639540496368</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.1229902096805769</v>
+        <v>-0.03273527251524428</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03652050614757956</v>
+        <v>-0.0172088087846109</v>
       </c>
     </row>
     <row r="8">
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4364127009986698</v>
+        <v>0.6229069891064934</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1222600383834697</v>
+        <v>-0.2304886913832773</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.08417654500053544</v>
+        <v>0.05389890825083962</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5012,22 +5012,22 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4325768781182674</v>
+        <v>0.76016183565662</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1651008900520076</v>
+        <v>-0.401147517369201</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1390727065953216</v>
+        <v>-0.05670337860192001</v>
       </c>
       <c r="O9" t="n">
         <v>-0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -5036,73 +5036,73 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1574510280963652</v>
+        <v>0.1877695501895166</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02691585709812528</v>
+        <v>-0.09120220074408446</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03521905659133234</v>
+        <v>-0.1412552413462852</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1048627604438015</v>
+        <v>-0.1280594842970837</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.02477445796860505</v>
+        <v>-0.2849924237822738</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.0266085246064047</v>
+        <v>-0.09326628726564136</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.07105075723151431</v>
+        <v>0.2222315190977919</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.05206607875585138</v>
+        <v>-0.1085995977872902</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.03925925811019379</v>
+        <v>0.1739503529415117</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5117,55 +5117,55 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4565639240459538</v>
+        <v>0.5862950665562959</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.01483221644763541</v>
+        <v>-0.195753071245347</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.14259154724045</v>
+        <v>-0.3456058233333751</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.02802216407627916</v>
+        <v>0.0892098685034375</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.0767627917934577</v>
+        <v>-0.02675939770961097</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.2210005319640361</v>
+        <v>0.05190717358735815</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,19 +5174,19 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.03697696096497962</v>
+        <v>-0.05751882551497325</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.02412516321265624</v>
+        <v>-0.06769168378369678</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0957952109796202</v>
+        <v>0.06563979802668818</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
@@ -5201,43 +5201,43 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.262977387409031</v>
+        <v>0.5415538224761839</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.007014187649297195</v>
+        <v>-0.2317898290575354</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0729577588668268</v>
+        <v>-0.05834386744495751</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1204097784851455</v>
+        <v>-0.2143393008471898</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01115003453073963</v>
+        <v>0.1865508745315096</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01647929252555992</v>
+        <v>-0.03776949184704866</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
@@ -5255,19 +5255,19 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.01075848988723854</v>
+        <v>-0.1241087920752982</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.05138775577135381</v>
+        <v>0.2148439690929947</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.0846237364191272</v>
+        <v>0.01805305815089667</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,28 +5276,28 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.1101978538685355</v>
+        <v>-0.1959219915676942</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02795376246541411</v>
+        <v>0.1839479678534581</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.02432707620095008</v>
+        <v>-0.02760201099442325</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
@@ -5309,46 +5309,46 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.1369275889431344</v>
+        <v>-0.2881727654336388</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.02705193792472179</v>
+        <v>0.01416984054523919</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03899167868768724</v>
+        <v>-0.1097888867877578</v>
       </c>
       <c r="DJ9" t="n">
         <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.04102429553835134</v>
+        <v>-0.1152625896426797</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.0921577845030614</v>
+        <v>0.1596627945339916</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.05045974928374376</v>
+        <v>0.05954446981563372</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
@@ -5360,25 +5360,25 @@
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.06489857043054807</v>
+        <v>0.01696740015864889</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.03431605098793519</v>
+        <v>-0.04010568933755559</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.04124955170766773</v>
+        <v>0.03468349319717069</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
         <v>0</v>
@@ -5387,52 +5387,52 @@
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.08522782202366673</v>
+        <v>-0.1871211580789953</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.03961721085029832</v>
+        <v>0.1205949645340095</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.05732087660831015</v>
+        <v>-0.01664072866861653</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.09141417003815153</v>
+        <v>-0.09006945341964696</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.03922352804181977</v>
+        <v>0.03697312378076693</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.02388402373576547</v>
+        <v>-0.1358474950923219</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5441,25 +5441,25 @@
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.111021318247276</v>
+        <v>-0.2279298519373604</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.02791561438486882</v>
+        <v>0.2072510289734306</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.02114534413813288</v>
+        <v>-0.05343248167643232</v>
       </c>
       <c r="FC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5468,19 +5468,19 @@
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02413317163026585</v>
+        <v>-0.1875899724285907</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.06713840594655165</v>
+        <v>0.1402634813326789</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.0808984636754793</v>
+        <v>-0.01808192701838869</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5489,49 +5489,49 @@
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.06168525562620482</v>
+        <v>-0.3352956319661995</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.1381350728665878</v>
+        <v>0.3400231466097192</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.0582806894589532</v>
+        <v>0.1917464180749557</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.004918809312884615</v>
+        <v>-0.286429285452208</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.0555991045602135</v>
+        <v>0.1905125569551358</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
@@ -5543,10 +5543,10 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7896572283882904</v>
+        <v>0.5934808219112925</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,13 +5563,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.09724943569593857</v>
+        <v>-0.001391162601149037</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4801103547756475</v>
+        <v>-0.351341102381747</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
@@ -5581,7 +5581,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7862291278148225</v>
+        <v>0.989222312454159</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,16 +5590,16 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.03762006579171671</v>
+        <v>-0.3186001248841479</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8108024257131298</v>
+        <v>-0.5386551199464851</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -5608,7 +5608,7 @@
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1132842841366111</v>
+        <v>0.1388543912970074</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -5617,25 +5617,25 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.165736665959958</v>
+        <v>-0.1235877993452758</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.04497996912847784</v>
+        <v>-0.1534068127939599</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.04006121745721534</v>
+        <v>0.05950294573750579</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -5644,10 +5644,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.03730960109521671</v>
+        <v>-0.335596285043086</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.02523393848985387</v>
+        <v>-0.01248862390082369</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5656,13 +5656,13 @@
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1691114258848674</v>
+        <v>0.09496026016714625</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
@@ -5671,13 +5671,13 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.07400135615353011</v>
+        <v>-0.03494656333792734</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.1908076001708986</v>
+        <v>-0.1255220061323424</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,10 +5686,10 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6791535627584835</v>
+        <v>0.9912649017464488</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,13 +5698,13 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.06784846483430823</v>
+        <v>-0.266066041340225</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.5545105244430468</v>
+        <v>-0.449496721476578</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
         <v>-0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.2135758827565682</v>
+        <v>-0.1094025284671624</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,40 +5725,40 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.17639221010928</v>
+        <v>0.07421706987819841</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.1740219637820641</v>
+        <v>-0.03839815958889962</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1793128249174742</v>
+        <v>0.2118658641040944</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.004965480991825745</v>
+        <v>0.1451423970323311</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-8.207899720864709e-05</v>
+        <v>0.07273328266258706</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,7 +5770,7 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.3898603636480943</v>
+        <v>0.5860080265032681</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -5779,10 +5779,10 @@
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.1089402438495041</v>
+        <v>-0.1283535458184499</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.2970971847311159</v>
+        <v>-0.2861579141631228</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5797,7 +5797,7 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.1677940148055812</v>
+        <v>-0.2547717058890044</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
@@ -5806,13 +5806,13 @@
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.03398383854159838</v>
+        <v>0.05161582395578654</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.142046889693274</v>
+        <v>0.1758753890825504</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
@@ -5824,22 +5824,22 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.004100011823788998</v>
+        <v>-0.2511542316397242</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.001550350905557011</v>
+        <v>0.04186937403523842</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.02723126931539167</v>
+        <v>0.06042007703025925</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
@@ -5848,49 +5848,49 @@
         <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1406216491391074</v>
+        <v>-0.2556871709370001</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.04688324013634841</v>
+        <v>0.01676940258872459</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.1746702004523784</v>
+        <v>0.1883372724803561</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.08331876198993519</v>
+        <v>-0.06810571733113911</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1131738862569511</v>
+        <v>-0.2279560178926304</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0.05552828535873072</v>
+        <v>0.07469678539065266</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
@@ -5899,55 +5899,55 @@
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.004670346733203089</v>
+        <v>-0.1259515172759061</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.02388871749658413</v>
+        <v>0.07908138994962505</v>
       </c>
       <c r="DS10" t="n">
-        <v>-2.358016954926391e-05</v>
+        <v>0.1255713539506271</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.1186267048178468</v>
+        <v>-0.1766089894121963</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.01355393993915582</v>
+        <v>-0.01946241899304349</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.07281284466190099</v>
+        <v>-0.1123662630803027</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
         <v>0</v>
@@ -5956,64 +5956,64 @@
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.1596292374703757</v>
+        <v>-0.01210433437653748</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
         <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.02266632135391921</v>
+        <v>-0.1052090213883236</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.1625280012402696</v>
+        <v>0.09921783003831809</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.05592109575613841</v>
+        <v>-0.06078620599075187</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.01969594055404902</v>
+        <v>-0.09200207356466501</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.04791468893062824</v>
+        <v>0.03668472516151875</v>
       </c>
       <c r="EU10" t="n">
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1344137421487105</v>
+        <v>-0.2754521946398847</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
@@ -6022,52 +6022,52 @@
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.03922102605259725</v>
+        <v>-0.01039645454523705</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.142530839603405</v>
+        <v>0.17081760624842</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.04344902130562239</v>
+        <v>0.2230131430274353</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02014927122568042</v>
+        <v>0.05403605072128495</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.1489896657469541</v>
+        <v>0.1474332667557591</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.08818304328001114</v>
+        <v>-0.1860320473429053</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,54 +6076,54 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.1847988795425745</v>
+        <v>0.05894327134887902</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.02786231107475442</v>
+        <v>0.06059053204574895</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
         <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.06853835577871248</v>
+        <v>-0.05884190041728199</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.134506346147751</v>
+        <v>0.05384216860488742</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.2051387585459637</v>
+        <v>-0.1545118731368322</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9124375384613524</v>
+        <v>0.2676330784304911</v>
       </c>
       <c r="C11" t="n">
         <v>-0</v>
@@ -6132,25 +6132,25 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09559970673416031</v>
+        <v>-0.1481766650566383</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2608976737366263</v>
+        <v>-0.08505385776306258</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8542145562941079</v>
+        <v>0.4853059301475505</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,7 +6159,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02438902305585929</v>
+        <v>-0.2923514785452734</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -6174,25 +6174,25 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.06717405162997284</v>
+        <v>0.05896411776975477</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2423816441277672</v>
+        <v>0.1010682019193266</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.131084730989732</v>
+        <v>-0.05536050735899789</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -6201,10 +6201,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.07838420328639652</v>
+        <v>-0.05007741383161049</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2345068263203097</v>
+        <v>0.04275679063797296</v>
       </c>
       <c r="AD11" t="n">
         <v>-0</v>
@@ -6213,61 +6213,61 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.0762217236553233</v>
+        <v>-0.1428623112297716</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.03441851712929778</v>
+        <v>-0.06428302924220829</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1061474602462894</v>
+        <v>0.0180671887419898</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.04092057206353567</v>
+        <v>-0.06958864609715165</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.03466588372795239</v>
+        <v>-0.08487776352326244</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.8053532117448846</v>
+        <v>0.4230937357837591</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.3555249725514837</v>
+        <v>-0.2321552537767894</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
@@ -6276,25 +6276,25 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.07571441732266736</v>
+        <v>-0.05251276781472957</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.1114054041256132</v>
+        <v>0.03303900586180816</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.2020689909903703</v>
+        <v>-0.003220739727159529</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,16 +6303,16 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.02971428210900054</v>
+        <v>0.03248285024384167</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.009203241287896593</v>
+        <v>0.1544978163378415</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,7 +6321,7 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1164845846802259</v>
+        <v>0.1489538366148972</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
@@ -6336,25 +6336,25 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0519921841821125</v>
+        <v>0.02672091150261923</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.4811297002840509</v>
+        <v>0.2270057378461978</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.1125230737979435</v>
+        <v>-0.06708614756204359</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
         <v>-0</v>
@@ -6363,49 +6363,49 @@
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.02575665785360905</v>
+        <v>0.05779930130685788</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.2237454737574341</v>
+        <v>-0.06579471359757504</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.05867831642146935</v>
+        <v>0.08883572334961308</v>
       </c>
       <c r="CI11" t="n">
         <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.1809394681573626</v>
+        <v>-0.06321007616374089</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.05504619581608389</v>
+        <v>-0.1538095400990202</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1248711127301497</v>
+        <v>0.001055746414048001</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
@@ -6414,13 +6414,13 @@
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.009860383284629693</v>
+        <v>0.02354788011593569</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.2377696976547401</v>
+        <v>-0.06854038524459354</v>
       </c>
       <c r="CX11" t="n">
         <v>-0</v>
@@ -6429,121 +6429,121 @@
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.06914893628880042</v>
+        <v>0.03527535978967526</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0.03543241183969065</v>
+        <v>0.03585925575420546</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.2521827491062154</v>
+        <v>-0.1735236189725069</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0.06508860096348637</v>
+        <v>-0.1221576772280661</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
         <v>-0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0.05180754205119136</v>
+        <v>-0.01156649613224173</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.1362012624299459</v>
+        <v>0.003454180601525676</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.005750825675808329</v>
+        <v>-0.06008237696624104</v>
       </c>
       <c r="DS11" t="n">
         <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.006464306138407768</v>
+        <v>0.1016655445420255</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.1912935051681879</v>
+        <v>-0.06753968223285463</v>
       </c>
       <c r="DY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.06148877020670131</v>
+        <v>-0.05745885510374543</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0.09244789017948719</v>
+        <v>-0.1260474683565638</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.1114158981032856</v>
+        <v>0.002271731495980363</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.05073510940896747</v>
+        <v>0.0121519383076786</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
@@ -6552,37 +6552,37 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>-0.03670091136969254</v>
+        <v>-0.07309581133314566</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1775825467648408</v>
+        <v>0.039855041409178</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.1659908270553308</v>
+        <v>0.01972227041551767</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>-0.007449497942732738</v>
+        <v>0.0470797824201409</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.2369197919900651</v>
+        <v>-0.1117152288401225</v>
       </c>
       <c r="EZ11" t="n">
         <v>0</v>
@@ -6591,25 +6591,25 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.1154745563659354</v>
+        <v>0.04991009413065339</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0.02432431489100056</v>
+        <v>0.0121501455000056</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.03658066506039972</v>
+        <v>0.1099286456171329</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,10 +6618,10 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.01636569070045835</v>
+        <v>-0.1434242209971183</v>
       </c>
       <c r="FL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
@@ -6633,25 +6633,25 @@
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0.1219778731001157</v>
+        <v>-0.003156392708718107</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.2285094271733714</v>
+        <v>-0.05350218643870392</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.213154584523489</v>
+        <v>0.2307292274194992</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>-0</v>
@@ -6660,22 +6660,22 @@
         <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0.183060046086167</v>
+        <v>0.0476247510073397</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.0975203873225194</v>
+        <v>-0.04734341710804203</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4710912653488064</v>
+        <v>0.04750403504362768</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,7 +6701,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2046901961649735</v>
+        <v>-0.01152476452123723</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
         <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.007853621829637074</v>
+        <v>-0.006227520682417899</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4057165749466082</v>
+        <v>0.06559111304565771</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,25 +6728,25 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2176154284123121</v>
+        <v>-0.03108822869611217</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.06142059858944812</v>
+        <v>-0.02119450595699542</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1158394751770186</v>
+        <v>0.009353524773246961</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
@@ -6755,16 +6755,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02580586041198331</v>
+        <v>0.00667415320804738</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.04083375595604836</v>
+        <v>-0.001429725339796455</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,7 +6773,7 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1758035736317312</v>
+        <v>-0.005670446652735367</v>
       </c>
       <c r="AD12" t="n">
         <v>-0</v>
@@ -6782,16 +6782,16 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.1224727093546701</v>
+        <v>-0.01732037951152134</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.01161982137730038</v>
+        <v>-0.001049114950267168</v>
       </c>
       <c r="AJ12" t="n">
         <v>-0</v>
@@ -6800,34 +6800,34 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0740738657735347</v>
+        <v>0.01038964426626868</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.02949696275775219</v>
+        <v>0.01166345803743555</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.05533196444654851</v>
+        <v>-0.002391467775424224</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.417412770217926</v>
+        <v>0.0465065607303952</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,25 +6836,25 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.03686887244178801</v>
+        <v>0.004119237429666606</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
         <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.03588582705249777</v>
+        <v>-0.005832471921394631</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.08272696292415983</v>
+        <v>-0.002592212366552015</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,16 +6863,16 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1931966193130564</v>
+        <v>-0.01900734120933965</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-0.05162487017478355</v>
+        <v>-0.001657893609107438</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.05930893196124712</v>
+        <v>-0.004227909878651247</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
@@ -6890,43 +6890,43 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0776362319171847</v>
+        <v>0.02531414881515537</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.02003671831839036</v>
+        <v>0.01022129283560076</v>
       </c>
       <c r="BT12" t="n">
         <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2501848770920686</v>
+        <v>0.03481685035291234</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
         <v>-0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.008919011298759685</v>
+        <v>0.01261035183572966</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0298916123720695</v>
+        <v>-0.004200449449274435</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.106098617200308</v>
+        <v>-0.01878916696538281</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.02358281400349414</v>
+        <v>0.004552869431906995</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6953,88 +6953,88 @@
         <v>0</v>
       </c>
       <c r="CK12" t="n">
-        <v>-0.004374166536911765</v>
+        <v>0.004200929497797707</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.03832333870684061</v>
+        <v>-0.01815880388952718</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1267692116350717</v>
+        <v>-0.003454804125876427</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0.001998128510986145</v>
+        <v>0.002042386350667684</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.09616160862667707</v>
+        <v>-0.01913021926106008</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.004335682047606522</v>
+        <v>0.004008916695394294</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>-0.01177733850943323</v>
+        <v>0.004751766761911121</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.1721383722102683</v>
+        <v>-0.01256738438340767</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08682120371039685</v>
+        <v>-0.01026316347408058</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
-        <v>-0.04598328725943202</v>
+        <v>-0.003883770180549891</v>
       </c>
       <c r="DM12" t="n">
         <v>-0</v>
@@ -7043,61 +7043,61 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.006769509984030727</v>
+        <v>-0.001725789273272847</v>
       </c>
       <c r="DP12" t="n">
         <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.05484088096683114</v>
+        <v>0.0001720268049204066</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT12" t="n">
         <v>0</v>
       </c>
       <c r="DU12" t="n">
-        <v>-0.004638283624451488</v>
+        <v>0.007424053877500785</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.053431797233202</v>
+        <v>-0.01179921238201746</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.0693271317600051</v>
+        <v>-0.004781230424296875</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.04073147701627769</v>
+        <v>-0.004311376754400293</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.08996777184590696</v>
+        <v>-0.003982687156439711</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.07821412132433167</v>
+        <v>-0.0002253027421724809</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,52 +7115,52 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0.02916394622604921</v>
+        <v>0.001919621756696526</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.05844977158481841</v>
+        <v>-0.01812917592470591</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.01624527038153707</v>
+        <v>0.001087493525807502</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0.001420375838872451</v>
+        <v>0.005416603350901809</v>
       </c>
       <c r="EW12" t="n">
         <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1005848162548132</v>
+        <v>-0.02134938415830141</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.01174953454441455</v>
+        <v>-0.00034699044439596</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,16 +7169,16 @@
         <v>-0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0.001356867073221091</v>
+        <v>0.00385004968224961</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.04827900316176969</v>
+        <v>0.01244701962366924</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
@@ -7187,16 +7187,16 @@
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.05296542861680146</v>
+        <v>-0.00636668202867633</v>
       </c>
       <c r="FL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.02024340353452489</v>
+        <v>0.002319885756403633</v>
       </c>
       <c r="FO12" t="n">
         <v>-0</v>
@@ -7205,7 +7205,7 @@
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01543824415344748</v>
+        <v>-0.01003889983562052</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,25 +7214,25 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0237427957797768</v>
+        <v>-0.0009674974583359102</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.002923557205233586</v>
+        <v>0.002266053931683138</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.07464997642407588</v>
+        <v>-0.01254348978374567</v>
       </c>
       <c r="GA12" t="n">
         <v>0</v>
@@ -7244,16 +7244,16 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>-0.05652794587616708</v>
+        <v>-0.008276291881066981</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,25 +7261,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2702912838627323</v>
+        <v>0.01720368434882814</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1054934075148222</v>
+        <v>-0.004249098980209451</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004576726381069439</v>
+        <v>0.001745391301487269</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7288,22 +7288,22 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2198853770278497</v>
+        <v>0.02588829852052166</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.08854673173902292</v>
+        <v>-0.004364790952508634</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.04984873405372747</v>
+        <v>-0.007156527186163708</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -7315,97 +7315,97 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.03220554537904734</v>
+        <v>0.006904550744184189</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.01042586294037256</v>
+        <v>0.003179664136612994</v>
       </c>
       <c r="V13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04606893033899524</v>
+        <v>0.0110693612234197</v>
       </c>
       <c r="X13" t="n">
         <v>-0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.09206668992985011</v>
+        <v>-0.002168518899565786</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.00486552686971979</v>
+        <v>-0.003440795366281273</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01090809188192679</v>
+        <v>-0.0255225641528496</v>
       </c>
       <c r="AG13" t="n">
         <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
         <v>-0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.03976156188317363</v>
+        <v>0.0120610743519694</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.02403898915860778</v>
+        <v>0.002392856554825687</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.01310458162085699</v>
+        <v>0.004810597864078951</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2066633692580593</v>
+        <v>0.0307816606984656</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.06159425373034457</v>
+        <v>0.006252776753979102</v>
       </c>
       <c r="AW13" t="n">
         <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.04222238100293722</v>
+        <v>-0.003124731114660065</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7420,22 +7420,22 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.07701932569997068</v>
+        <v>-0.004373178507736501</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.0669373926249021</v>
+        <v>-0.006855630958265758</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.08326232115916296</v>
+        <v>-0.01261051661354017</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI13" t="n">
         <v>-0</v>
@@ -7444,28 +7444,28 @@
         <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.03922143299574027</v>
+        <v>0.004447583485541588</v>
       </c>
       <c r="BN13" t="n">
-        <v>-0.04610431381525728</v>
+        <v>0.001031949328631171</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.02677604891025485</v>
+        <v>0.004019130315394534</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7477,49 +7477,49 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.08475183383924009</v>
+        <v>0.02401321361906027</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0.1075671911332393</v>
+        <v>0.005966791903232453</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.02845306268292037</v>
+        <v>0.01136411729333206</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.06244234883672542</v>
+        <v>-0.006447416688704963</v>
       </c>
       <c r="CF13" t="n">
-        <v>-0.00107544301266719</v>
+        <v>0.002878571386670605</v>
       </c>
       <c r="CG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.00613808407776136</v>
+        <v>-0.000632221251589238</v>
       </c>
       <c r="CI13" t="n">
         <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
@@ -7531,43 +7531,43 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.01049449992626484</v>
+        <v>-0.01768189000364896</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0.002130780132696616</v>
+        <v>-0.003199343869279261</v>
       </c>
       <c r="CP13" t="n">
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.007917146017830289</v>
+        <v>0.006451779314546929</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
       </c>
       <c r="CT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.05392090265536812</v>
+        <v>-0.00623393129178188</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0.0115714729735867</v>
+        <v>0.002350774195818458</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.02127049528958345</v>
+        <v>-0.002737054948293129</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
@@ -7585,22 +7585,22 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.06621369962480785</v>
+        <v>-0.00899012737117927</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.002337616543583512</v>
+        <v>0.005776947060593142</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.01364576154070779</v>
+        <v>-0.007852642902047241</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
       </c>
       <c r="DK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
@@ -7609,19 +7609,19 @@
         <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.008046058618139063</v>
+        <v>-0.0006179071979501828</v>
       </c>
       <c r="DP13" t="n">
-        <v>-0.03153246575185505</v>
+        <v>-0.006042807845029852</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01899972062022873</v>
+        <v>0.00528465987624425</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
@@ -7633,25 +7633,25 @@
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.07602019564491927</v>
+        <v>-0.01216602204072815</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.009032779438749956</v>
+        <v>-0.0002764544474909292</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0052755013053967</v>
+        <v>-0.003540420513814817</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
@@ -7660,25 +7660,25 @@
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02881903082012044</v>
+        <v>0.0005090965068074692</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0006312915280258072</v>
+        <v>0.004520851244013494</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.02096486096636332</v>
+        <v>-0.004473759387044331</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7687,49 +7687,49 @@
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.05027865717491811</v>
+        <v>-0.006458989734918708</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.03099546052736537</v>
+        <v>-0.001161361127926933</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.01802245750474361</v>
+        <v>0.001596336496542843</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.05680942620833573</v>
+        <v>-0.008449850551760304</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0.003330138602024208</v>
+        <v>0.002036228193397048</v>
       </c>
       <c r="FA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.007123559294047027</v>
+        <v>-0.001580360933198314</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
@@ -7738,7 +7738,7 @@
         <v>-0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
         <v>-0</v>
@@ -7747,46 +7747,46 @@
         <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.01500028279327427</v>
+        <v>-0.001241084812437704</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.004736339562536831</v>
+        <v>0.00725616506002589</v>
       </c>
       <c r="FJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.06053773106781415</v>
+        <v>0.006402197172839071</v>
       </c>
       <c r="FL13" t="n">
         <v>-0</v>
       </c>
       <c r="FM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01169703809469666</v>
+        <v>-0.003290179333000005</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.03839508970272475</v>
+        <v>-0.002366205881505173</v>
       </c>
       <c r="FS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.02286639539670951</v>
+        <v>0.007760334300738703</v>
       </c>
       <c r="FU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,31 +7795,31 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.02108894758841711</v>
+        <v>-0.009776494087160088</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0.009871620272156469</v>
+        <v>-0.003142297342036255</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -8965,10 +8965,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.1030235892895528</v>
+        <v>-0.1724544283576091</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8285283075101392</v>
+        <v>0.3497355738485313</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2414521541289058</v>
+        <v>-0.2182485734689576</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.158392189651844</v>
+        <v>-0.1209902380142184</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6193755452703801</v>
+        <v>0.4103544720483975</v>
       </c>
       <c r="L16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2808138460182866</v>
+        <v>-0.2936579907951176</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -9019,49 +9019,49 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.006424122077153116</v>
+        <v>0.05664052558018271</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1498721296715293</v>
+        <v>0.03504987421086276</v>
       </c>
       <c r="U16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03875980000131445</v>
+        <v>-0.1207150189064193</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.04265992508014846</v>
+        <v>-0.03328567854827205</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1782433572558032</v>
+        <v>0.07627019968859192</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.07028858481827339</v>
+        <v>-0.2828981792910091</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
@@ -9070,49 +9070,49 @@
         <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.05360548081793667</v>
+        <v>-0.0447055318596386</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.1033713700661508</v>
+        <v>0.05471570525175179</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.0454916496613532</v>
+        <v>-0.2499143150325506</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0.01297963833460063</v>
+        <v>0.02523884405473992</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.5802687936147327</v>
+        <v>0.4569562082066596</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1457918691933472</v>
+        <v>-0.4751923409512532</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -9124,22 +9124,22 @@
         <v>-0</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0.02951729368028931</v>
+        <v>-0.03762417760083699</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.1300787652963142</v>
+        <v>0.1658591745939283</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.2417319048519269</v>
+        <v>0.1585465887885798</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
@@ -9148,31 +9148,31 @@
         <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0233835471354444</v>
+        <v>0.0186575058702719</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.1228547145237824</v>
+        <v>0.3655730470907456</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.1202583028247091</v>
+        <v>0.1934853464277761</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
@@ -9181,22 +9181,22 @@
         <v>-0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.009498726418643974</v>
+        <v>0.04816688733292988</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.3399335900399296</v>
+        <v>0.1870928140999293</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.0384426626729837</v>
+        <v>-0.1559634797334668</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9208,49 +9208,49 @@
         <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.01698499269037195</v>
+        <v>0.06455499581674043</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.1291503228567244</v>
+        <v>-0.03521308150385833</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.009055596932915544</v>
+        <v>0.09729488853111798</v>
       </c>
       <c r="CI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>-0.1105943280113055</v>
+        <v>-0.1496107041807438</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.05736224547522696</v>
+        <v>-0.3741337283609932</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.2526563094681473</v>
+        <v>-0.02247031975865301</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9259,94 +9259,94 @@
         <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.009351487353691694</v>
+        <v>0.03587927350478305</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.1144743467087338</v>
+        <v>-0.03092382273199725</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.006459107078569082</v>
+        <v>0.03244655608629068</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
         <v>0</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0.03297340390898228</v>
+        <v>-0.04909933523398274</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.2334527562169257</v>
+        <v>-0.1761771799870934</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
         <v>-0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.08858409009080577</v>
+        <v>-0.04084027060838166</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL16" t="n">
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0.01577137947316656</v>
+        <v>-0.09453064385128317</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.02644150260474605</v>
+        <v>-0.008941953716941444</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.0400221375990043</v>
+        <v>-0.07740781177764539</v>
       </c>
       <c r="DS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT16" t="n">
         <v>0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
-        <v>-0.006912324072061461</v>
+        <v>0.08439661343924672</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.1500722425223427</v>
+        <v>-0.01707931940946061</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
@@ -9355,34 +9355,34 @@
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.08106793992968868</v>
+        <v>-0.1472981731439371</v>
       </c>
       <c r="EB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC16" t="n">
         <v>0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>-0.0189091154871905</v>
+        <v>-0.00359652150273712</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.08988636023061211</v>
+        <v>0.1100084722540024</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
         <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.1030622664043265</v>
+        <v>-0.005568995139428629</v>
       </c>
       <c r="EK16" t="n">
         <v>-0</v>
@@ -9391,112 +9391,112 @@
         <v>-0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>-0.02072866488113738</v>
+        <v>-0.03771390977021172</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.1036150086209641</v>
+        <v>0.03845791133345811</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.07121160915617848</v>
+        <v>0.07095853592339588</v>
       </c>
       <c r="ET16" t="n">
         <v>-0</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX16" t="n">
-        <v>-0.004296178833598676</v>
+        <v>0.04161022717142283</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.1242077578541294</v>
+        <v>-0.09230527735011579</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.02109431844777622</v>
+        <v>0.03810723047255326</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0.01183042190480619</v>
+        <v>0.02988545551729768</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.0590969876219888</v>
+        <v>0.1115118150477062</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.06317655705183579</v>
+        <v>-0.2155954427000649</v>
       </c>
       <c r="FL16" t="n">
         <v>-0</v>
       </c>
       <c r="FM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>-0.02912566105188834</v>
+        <v>0.06268744393611676</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.04646807916857813</v>
+        <v>-0.09401824395436371</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.07951849866036313</v>
+        <v>0.362114518358682</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW16" t="n">
         <v>0</v>
@@ -9505,10 +9505,10 @@
         <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0.08923344350431392</v>
+        <v>0.08660910443618862</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.07314189295924445</v>
+        <v>0.008158603916996104</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
@@ -9517,10 +9517,10 @@
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
